--- a/06_附件资料/表格相关/零星组织导入数据.xlsx
+++ b/06_附件资料/表格相关/零星组织导入数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13500"/>
+    <workbookView windowWidth="30720" windowHeight="13044"/>
   </bookViews>
   <sheets>
     <sheet name="组织导入模板" sheetId="2" r:id="rId1"/>
